--- a/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%2375</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.87%663,000</t>
+          <t>8.98%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>663000</v>
+        <v>753000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.21%13925</t>
+          <t>-3.88%13385</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>13925</v>
+        <v>13385</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.48%91,000</t>
+          <t>5.59%80,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.48%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>91000</v>
+        <v>80000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.77%3700</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3700</v>
+        <v>3790</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.93%254,000</t>
+          <t>4.62%249,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>254000</v>
+        <v>249000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.79%5985</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5985</v>
+        <v>5680</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.04%136,000</t>
+          <t>4.09%136,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.13%1745</t>
+          <t>+0.29%1750</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.60%404,000</t>
+          <t>3.54%404,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.88%1140</t>
+          <t>-4.82%1085</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1140</v>
+        <v>1085</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.21%563,000</t>
+          <t>3.22%563,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.73%2780</t>
+          <t>+5.04%2920</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2780</v>
+        <v>2920</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.10%228,600</t>
+          <t>3.19%228,600</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+7.48%517</t>
+          <t>+2.13%528</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+7.48%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.66%1,096,000</t>
+          <t>2.84%1,096,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.61%246.5</t>
+          <t>-0.41%245.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>246.5</v>
+        <v>245.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.16%6455</t>
+          <t>-0.77%6405</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6455</v>
+        <v>6405</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.38%73,000</t>
+          <t>2.37%73,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.8%186</t>
+          <t>+3.23%192</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.29%2,416,000</t>
+          <t>2.26%2,416,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.55%2985</t>
+          <t>-3.27%5465</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2985</v>
+        <v>5465</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.10%134,000</t>
+          <t>2.04%72,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>134000</v>
+        <v>72000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.44%1025</t>
+          <t>+2.55%181</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1025</v>
+        <v>181</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.06%393,000</t>
+          <t>2.03%2,293,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>393000</v>
+        <v>2293000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.53%1995</t>
+          <t>-5.85%965</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1995</v>
+        <v>965</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.96%197,000</t>
+          <t>2.02%393,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>197000</v>
+        <v>393000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:26</t>
+          <t>2026-08-21 14:49:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.52%5650</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5650</v>
+        <v>2865</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.91%72,000</t>
+          <t>2.01%134,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>72000</v>
+        <v>134000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.56%5600</t>
+          <t>+4.01%2075</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5600</v>
+        <v>2075</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.90%69,000</t>
+          <t>1.97%197,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>69000</v>
+        <v>197000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.94%2105</t>
+          <t>-3.66%5395</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2105</v>
+        <v>5395</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.87%174,000</t>
+          <t>1.94%69,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>174000</v>
+        <v>69000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.16%6380</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6380</v>
+        <v>2035</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.77%55,000</t>
+          <t>1.84%174,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>55000</v>
+        <v>174000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.78%6325</t>
+          <t>+0.31%6400</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6325</v>
+        <v>6400</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.67%52,000</t>
+          <t>1.76%55,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>52000</v>
+        <v>55000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5.06%176.5</t>
+          <t>-1.42%554</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+5.06%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>176.5</v>
+        <v>554</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.65%1,942,000</t>
+          <t>1.68%595,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1942000</v>
+        <v>595000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.21%327</t>
+          <t>-0.53%5600</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>327</v>
+        <v>5600</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.65%987,000</t>
+          <t>1.67%59,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>987000</v>
+        <v>59000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.94%2140</t>
+          <t>-1.11%6255</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2140</v>
+        <v>6255</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.59%148,000</t>
+          <t>1.65%52,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>148000</v>
+        <v>52000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+6.33%5630</t>
+          <t>-5.08%1495</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+6.33%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5630</v>
+        <v>1495</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.58%59,000</t>
+          <t>1.65%209,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>59000</v>
+        <v>209000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.34%590</t>
+          <t>-1.68%321.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>590</v>
+        <v>321.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.56%526,000</t>
+          <t>1.62%987,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>526000</v>
+        <v>987000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.43%562</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>562</v>
+        <v>2100</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.50%514,000</t>
+          <t>1.59%148,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>514000</v>
+        <v>148000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.31%63.4</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>63.4</v>
+        <v>587</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.48%4,525,000</t>
+          <t>1.56%526,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4525000</v>
+        <v>526000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.51%15750</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>15750</v>
+        <v>15350</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.46%18,300</t>
+          <t>1.45%18,300</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+5%1575</t>
+          <t>+2.52%65</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1575</v>
+        <v>65</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.42%187,000</t>
+          <t>1.44%4,525,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>187000</v>
+        <v>4525000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5904寶雅國際</t>
+          <t>6213聯茂電子</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.69%75.9</t>
+          <t>+0.59%513</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>75.90000000000001</v>
+        <v>513</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.23%3,124,500</t>
+          <t>1.23%482,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3124500</v>
+        <v>482000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:28</t>
+          <t>2026-08-21 14:49:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2376技嘉科技</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.29%344</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>344</v>
+        <v>1135</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.22%694,000</t>
+          <t>1.22%203,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>694000</v>
+        <v>203000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2884玉山金融控股</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.19%37.35</t>
+          <t>-1.31%339.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>37.35</v>
+        <v>339.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.21%6,340,622</t>
+          <t>1.20%694,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6340622</v>
+        <v>694000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>2884玉山金融控股</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.27%1195</t>
+          <t>+1.74%38</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1195</v>
+        <v>38</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.21%203,000</t>
+          <t>1.19%6,340,622</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>203000</v>
+        <v>6340622</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6213聯茂電子</t>
+          <t>5904寶雅國際</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+5.37%510</t>
+          <t>-1.84%74.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+5.37%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>510</v>
+        <v>74.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.18%482,000</t>
+          <t>1.19%3,124,500</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>482000</v>
+        <v>3124500</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.99%205.5</t>
+          <t>+0.24%206</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>205.5</v>
+        <v>206</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.17%1,147,000</t>
+          <t>1.18%1,147,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.31%463</t>
+          <t>-4.75%441</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.06%461,000</t>
+          <t>1.07%461,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-3.96%1090</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1135</v>
+        <v>1090</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.04%181,000</t>
+          <t>1.03%181,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8210勤誠興業</t>
+          <t>3293鈊象電子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.13%964</t>
+          <t>-3.43%732</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>964</v>
+        <v>732</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.96%193,000</t>
+          <t>0.96%252,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>193000</v>
+        <v>252000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.1%180</t>
+          <t>-2.5%175.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>180</v>
+        <v>175.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.96%1,041,000</t>
+          <t>0.94%1,041,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3293鈊象電子</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.2%758</t>
+          <t>-2.07%944</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>758</v>
+        <v>944</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.95%252,000</t>
+          <t>0.93%193,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>252000</v>
+        <v>193000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.04%485.5</t>
+          <t>-5.46%459</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-5.46%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>485.5</v>
+        <v>459</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.24%851</t>
+          <t>-4.7%811</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>851</v>
+        <v>811</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.63%5515</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5515</v>
+        <v>5610</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.73%26,000</t>
+          <t>0.72%26,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.97%208.5</t>
+          <t>-2.64%203</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>208.5</v>
+        <v>203</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.5%602</t>
+          <t>-4.65%574</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-4.65%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>602</v>
+        <v>574</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:29</t>
+          <t>2026-08-21 14:49:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.21%2210</t>
+          <t>-4.59%1765</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2210</v>
+        <v>1765</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.50%44,000</t>
+          <t>0.50%54,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>44000</v>
+        <v>54000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:30</t>
+          <t>2026-08-21 14:49:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%1850</t>
+          <t>-2.49%2155</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1850</v>
+        <v>2155</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.49%54,000</t>
+          <t>0.49%44,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>54000</v>
+        <v>44000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:30</t>
+          <t>2026-08-21 14:49:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.9%710</t>
+          <t>-10%639</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>710</v>
+        <v>639</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.47%134,000</t>
+          <t>0.48%134,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:30</t>
+          <t>2026-08-21 14:49:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+2.27%2250</t>
+          <t>+1.11%2275</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.36%32,336</t>
+          <t>0.37%32,336</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:30</t>
+          <t>2026-08-21 14:49:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3533嘉澤端子工業</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.62%1610</t>
+          <t>-1.93%1525</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1610</v>
+        <v>1525</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.29%35,000</t>
+          <t>0.30%38,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:30</t>
+          <t>2026-08-21 14:49:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,38 +3493,38 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3533嘉澤端子工業</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.63%1555</t>
+          <t>-0.93%1595</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.29%38,000</t>
+          <t>0.28%35,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:31</t>
+          <t>2026-08-21 14:54:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:32</t>
+          <t>2026-08-21 14:54:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:33</t>
+          <t>2026-08-21 14:54:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:35</t>
+          <t>2026-08-21 14:54:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:35</t>
+          <t>2026-08-21 14:54:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:35</t>
+          <t>2026-08-21 14:54:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:35</t>
+          <t>2026-08-21 14:54:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:49:35</t>
+          <t>2026-08-21 14:54:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:46</t>
+          <t>2026-08-21 17:27:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:48</t>
+          <t>2026-08-21 17:27:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:49</t>
+          <t>2026-08-21 17:27:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:50</t>
+          <t>2026-08-21 17:27:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:50</t>
+          <t>2026-08-21 17:27:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:50</t>
+          <t>2026-08-21 17:27:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:50</t>
+          <t>2026-08-21 17:27:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:50</t>
+          <t>2026-08-21 17:27:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
